--- a/Unity/Assets/Config/Excel/OccupationTwoConfig.xlsx
+++ b/Unity/Assets/Config/Excel/OccupationTwoConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="1">
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -82,9 +82,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
+  </si>
+  <si>
+    <t>OccupationName</t>
+  </si>
+  <si>
+    <t>OccDes</t>
+  </si>
+  <si>
+    <t>SkillID</t>
+  </si>
+  <si>
+    <t>ShowTalentSkill</t>
+  </si>
+  <si>
+    <t>Capacitys</t>
+  </si>
+  <si>
+    <t>WeaponType</t>
+  </si>
+  <si>
+    <t>ArmorMastery</t>
+  </si>
+  <si>
+    <t>ShowPassiveSkill</t>
+  </si>
+  <si>
+    <t>JueXingSkill</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>##</t>
   </si>
   <si>
     <t>职业名称</t>
@@ -131,42 +176,6 @@
     <t>觉醒技能</t>
   </si>
   <si>
-    <t>OccupationName</t>
-  </si>
-  <si>
-    <t>OccDes</t>
-  </si>
-  <si>
-    <t>SkillID</t>
-  </si>
-  <si>
-    <t>ShowTalentSkill</t>
-  </si>
-  <si>
-    <t>Capacitys</t>
-  </si>
-  <si>
-    <t>WeaponType</t>
-  </si>
-  <si>
-    <t>ArmorMastery</t>
-  </si>
-  <si>
-    <t>ShowPassiveSkill</t>
-  </si>
-  <si>
-    <t>JueXingSkill</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>逐风者</t>
   </si>
   <si>
@@ -363,7 +372,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,7 +380,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -555,27 +564,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -584,8 +575,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="50">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -835,48 +831,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799920651875362"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -885,6 +839,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -902,17 +867,6 @@
       <bottom style="thin">
         <color theme="0"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1203,955 +1157,957 @@
     <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="341" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="341" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="341" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="341" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="341" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2563,7 +2519,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{D58D416F-972A-4460-BC73-B929113E61B5}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{E68657F2-5AAA-418C-9AA1-278ED9BF1575}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2863,405 +2819,412 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L14"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="9.375" customWidth="1"/>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="71.375" customWidth="1"/>
-    <col min="6" max="6" width="68" customWidth="1"/>
-    <col min="7" max="7" width="56.25" customWidth="1"/>
-    <col min="8" max="8" width="22.375" customWidth="1"/>
-    <col min="9" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="23.75" customWidth="1"/>
-    <col min="11" max="11" width="46.25" customWidth="1"/>
-    <col min="12" max="12" width="68.375" customWidth="1"/>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="71.375" customWidth="1"/>
+    <col min="5" max="5" width="68" customWidth="1"/>
+    <col min="6" max="6" width="56.25" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="18.875" customWidth="1"/>
+    <col min="9" max="9" width="23.75" customWidth="1"/>
+    <col min="10" max="10" width="46.25" customWidth="1"/>
+    <col min="11" max="11" width="68.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1"/>
-    <row r="3" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C3" s="2" t="s">
+    <row r="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="K3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6" t="s">
+    <row r="4" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B4" s="8">
+        <v>101</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+      <c r="I4" s="10">
+        <v>12</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B5" s="8">
+        <v>102</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <v>12</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B6" s="8">
+        <v>103</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="10">
+        <v>2</v>
+      </c>
+      <c r="I6" s="10">
+        <v>13</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B7" s="8">
+        <v>201</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="10">
+        <v>3</v>
+      </c>
+      <c r="I7" s="10">
         <v>11</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="J7" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B8" s="8">
+        <v>202</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="10">
+        <v>4</v>
+      </c>
+      <c r="I8" s="10">
+        <v>11</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B9" s="8">
+        <v>203</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="10">
+        <v>4</v>
+      </c>
+      <c r="I9" s="10">
+        <v>13</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B10" s="8">
+        <v>301</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="10">
+        <v>5</v>
+      </c>
+      <c r="I10" s="10">
+        <v>11</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B11" s="8">
+        <v>302</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="10">
+        <v>5</v>
+      </c>
+      <c r="I11" s="10">
         <v>12</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="J11" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="2:11">
+      <c r="B12" s="8">
+        <v>303</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="10">
+        <v>5</v>
+      </c>
+      <c r="I12" s="10">
         <v>13</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C6" s="8">
-        <v>101</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="10">
-        <v>1</v>
-      </c>
-      <c r="J6" s="10">
-        <v>12</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C7" s="8">
-        <v>102</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="10">
-        <v>1</v>
-      </c>
-      <c r="J7" s="10">
-        <v>12</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C8" s="8">
-        <v>103</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="10">
-        <v>2</v>
-      </c>
-      <c r="J8" s="10">
-        <v>13</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C9" s="8">
-        <v>201</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="10">
-        <v>3</v>
-      </c>
-      <c r="J9" s="10">
-        <v>11</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C10" s="8">
-        <v>202</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="10">
-        <v>4</v>
-      </c>
-      <c r="J10" s="10">
-        <v>11</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C11" s="8">
-        <v>203</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="10">
-        <v>4</v>
-      </c>
-      <c r="J11" s="10">
-        <v>13</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C12" s="8">
-        <v>301</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" s="10">
-        <v>5</v>
-      </c>
-      <c r="J12" s="10">
-        <v>11</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C13" s="8">
-        <v>302</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="10">
-        <v>5</v>
-      </c>
-      <c r="J13" s="10">
-        <v>12</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C14" s="8">
-        <v>303</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="I14" s="10">
-        <v>5</v>
-      </c>
-      <c r="J14" s="10">
-        <v>13</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>83</v>
+      <c r="J12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
